--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91743</v>
+        <v>91744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91744</v>
+        <v>91745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91745</v>
+        <v>91751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91751</v>
+        <v>91752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91752</v>
+        <v>91758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79613</v>
+        <v>79619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91758</v>
+        <v>91765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91765</v>
+        <v>91766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83439</v>
+        <v>83452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79619</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91766</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34907-2023 artfynd.xlsx
+++ b/artfynd/A 34907-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136183990</v>
       </c>
       <c r="B2" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136183988</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136183994</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136183989</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136183993</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
